--- a/modelo/planilha-modelo.xlsx
+++ b/modelo/planilha-modelo.xlsx
@@ -16,8 +16,9 @@
     <sheet name="Despesas Casal" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Parcelas" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Investimentos" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Premissas" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Lançamentos" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Cartões" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Premissas" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Lançamentos" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="167">
   <si>
     <t xml:space="preserve">Planilha financeira do casal — guia rápido</t>
   </si>
@@ -88,6 +89,12 @@
     <t xml:space="preserve">Em Parcelas, Investimentos e Lançamentos: Rodrigo, Esposa ou Casal (vazio = Casal).</t>
   </si>
   <si>
+    <t xml:space="preserve">Cartões</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadastre os cartões na aba Cartões e marque na coluna 'Cartão' (Despesas e Parcelas) o que é cobrado em cada um. Vazio = Pix/débito/boleto. O painel monta a fatura de cada cartão.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lançamentos</t>
   </si>
   <si>
@@ -187,6 +194,9 @@
     <t xml:space="preserve">Tipo</t>
   </si>
   <si>
+    <t xml:space="preserve">Cartão</t>
+  </si>
+  <si>
     <t xml:space="preserve">Celular</t>
   </si>
   <si>
@@ -196,6 +206,9 @@
     <t xml:space="preserve">Fixa</t>
   </si>
   <si>
+    <t xml:space="preserve">Nubank Rodrigo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plano de saúde</t>
   </si>
   <si>
@@ -229,6 +242,9 @@
     <t xml:space="preserve">Pilates</t>
   </si>
   <si>
+    <t xml:space="preserve">Itaú Esposa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transporte (app/ônibus)</t>
   </si>
   <si>
@@ -347,6 +363,18 @@
   </si>
   <si>
     <t xml:space="preserve">Previdência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fechamento (dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vencimento (dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vazio na coluna 'Cartão' das despesas = Pix, débito ou boleto. No cartão, o gasto entra na fatura do mês seguinte.</t>
   </si>
   <si>
     <t xml:space="preserve">Chave</t>
@@ -514,8 +542,8 @@
     <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00;&quot;-R$ &quot;#,##0.00;\-"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="@"/>
-    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="@"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -678,7 +706,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -759,11 +787,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -775,7 +807,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1031,7 +1063,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1120,7 +1152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
@@ -1137,100 +1169,108 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="A16" s="2"/>
       <c r="B16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="7" t="n">
+      <c r="A17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="7" t="n">
         <f aca="false">SUM('Receitas Rodrigo'!H2:H1000)</f>
         <v>10311.0833333333</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="7" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="7" t="n">
         <f aca="false">SUM('Receitas Esposa'!H2:H1000)</f>
         <v>6444.41666666667</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="7" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="7" t="n">
         <f aca="false">SUM('Despesas Rodrigo'!I2:I1000)</f>
         <v>1880</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="7" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="7" t="n">
         <f aca="false">SUM('Despesas Esposa'!I2:I1000)</f>
         <v>1665</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="7" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="7" t="n">
         <f aca="false">SUM('Despesas Casal'!J2:J1000)</f>
         <v>5840</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="7" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="7" t="n">
         <f aca="false">SUM(Parcelas!D2:D1000)</f>
         <v>1050</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="7" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="7" t="n">
         <f aca="false">SUM(Investimentos!D2:D1000)</f>
         <v>1600</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="9" t="n">
-        <f aca="false">B17+B18-B19-B20-B21-B22-B23</f>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <f aca="false">B18+B19-B20-B21-B22-B23-B24</f>
         <v>4720.5</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-    </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="A26" s="2"/>
       <c r="B26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1244,6 +1284,247 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4" type="list">
+      <formula1>"Proporcional à renda,Igual (50/50),Percentual fixo"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1261,22 +1542,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1284,16 +1565,16 @@
         <v>46144</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F2" s="13" t="n">
         <v>280</v>
@@ -1304,16 +1585,16 @@
         <v>46144</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>299.19</v>
@@ -1324,16 +1605,16 @@
         <v>46144</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>683.05</v>
@@ -1344,16 +1625,16 @@
         <v>46144</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>484.2</v>
@@ -1364,16 +1645,16 @@
         <v>46145</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>248.36</v>
@@ -1384,16 +1665,16 @@
         <v>46145</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>183.25</v>
@@ -1404,16 +1685,16 @@
         <v>46146</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="D8" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>167.86</v>
@@ -1424,16 +1705,16 @@
         <v>46147</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>8200</v>
@@ -1444,16 +1725,16 @@
         <v>46147</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>5800</v>
@@ -1464,16 +1745,16 @@
         <v>46147</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>650</v>
@@ -1484,16 +1765,16 @@
         <v>46147</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>450</v>
@@ -1504,16 +1785,16 @@
         <v>46152</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>320</v>
@@ -1524,16 +1805,16 @@
         <v>46153</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>60</v>
@@ -1544,16 +1825,16 @@
         <v>46154</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F15" s="13" t="n">
         <v>55</v>
@@ -1564,16 +1845,16 @@
         <v>46155</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>120</v>
@@ -1584,16 +1865,16 @@
         <v>46155</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>90</v>
@@ -1604,16 +1885,16 @@
         <v>46156</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F18" s="13" t="n">
         <v>480</v>
@@ -1624,16 +1905,16 @@
         <v>46157</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F19" s="13" t="n">
         <v>280</v>
@@ -1644,16 +1925,16 @@
         <v>46159</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>271.76</v>
@@ -1664,16 +1945,16 @@
         <v>46160</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>2100</v>
@@ -1684,16 +1965,16 @@
         <v>46161</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F22" s="13" t="n">
         <v>580</v>
@@ -1704,16 +1985,16 @@
         <v>46163</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>377.69</v>
@@ -1724,16 +2005,16 @@
         <v>46163</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F24" s="13" t="n">
         <v>120</v>
@@ -1744,16 +2025,16 @@
         <v>46163</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F25" s="13" t="n">
         <v>1685.12</v>
@@ -1764,16 +2045,16 @@
         <v>46169</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F26" s="13" t="n">
         <v>258.59</v>
@@ -1784,16 +2065,16 @@
         <v>46175</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F27" s="13" t="n">
         <v>60</v>
@@ -1804,16 +2085,16 @@
         <v>46175</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="D28" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F28" s="13" t="n">
         <v>149.46</v>
@@ -1824,16 +2105,16 @@
         <v>46177</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F29" s="13" t="n">
         <v>263.16</v>
@@ -1844,16 +2125,16 @@
         <v>46177</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F30" s="13" t="n">
         <v>2100</v>
@@ -1864,16 +2145,16 @@
         <v>46178</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F31" s="13" t="n">
         <v>8200</v>
@@ -1884,16 +2165,16 @@
         <v>46178</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F32" s="13" t="n">
         <v>5800</v>
@@ -1904,16 +2185,16 @@
         <v>46178</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F33" s="13" t="n">
         <v>421.13</v>
@@ -1924,16 +2205,16 @@
         <v>46178</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F34" s="13" t="n">
         <v>259.07</v>
@@ -1944,16 +2225,16 @@
         <v>46178</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F35" s="13" t="n">
         <v>450</v>
@@ -1964,16 +2245,16 @@
         <v>46183</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F36" s="13" t="n">
         <v>580</v>
@@ -1984,16 +2265,16 @@
         <v>46183</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F37" s="13" t="n">
         <v>320</v>
@@ -2004,16 +2285,16 @@
         <v>46188</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F38" s="13" t="n">
         <v>385.85</v>
@@ -2024,16 +2305,16 @@
         <v>46188</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F39" s="13" t="n">
         <v>280</v>
@@ -2044,16 +2325,16 @@
         <v>46189</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F40" s="13" t="n">
         <v>120</v>
@@ -2064,16 +2345,16 @@
         <v>46191</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F41" s="13" t="n">
         <v>650</v>
@@ -2084,16 +2365,16 @@
         <v>46191</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F42" s="13" t="n">
         <v>280</v>
@@ -2104,16 +2385,16 @@
         <v>46191</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F43" s="13" t="n">
         <v>480</v>
@@ -2124,16 +2405,16 @@
         <v>46192</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F44" s="13" t="n">
         <v>55</v>
@@ -2144,16 +2425,16 @@
         <v>46192</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F45" s="13" t="n">
         <v>90</v>
@@ -2164,16 +2445,16 @@
         <v>46194</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F46" s="13" t="n">
         <v>179.03</v>
@@ -2184,16 +2465,16 @@
         <v>46195</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F47" s="13" t="n">
         <v>1652.3</v>
@@ -2204,16 +2485,16 @@
         <v>46196</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F48" s="13" t="n">
         <v>219.73</v>
@@ -2224,16 +2505,16 @@
         <v>46198</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F49" s="13" t="n">
         <v>614.68</v>
@@ -2244,16 +2525,16 @@
         <v>46200</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F50" s="13" t="n">
         <v>327.84</v>
@@ -2264,16 +2545,16 @@
         <v>46201</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F51" s="13" t="n">
         <v>120</v>
@@ -2284,16 +2565,16 @@
         <v>46206</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F52" s="13" t="n">
         <v>262.44</v>
@@ -2304,16 +2585,16 @@
         <v>46206</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F53" s="13" t="n">
         <v>1801.33</v>
@@ -2324,16 +2605,16 @@
         <v>46207</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F54" s="13" t="n">
         <v>204.95</v>
@@ -2344,16 +2625,16 @@
         <v>46208</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F55" s="13" t="n">
         <v>8200</v>
@@ -2364,16 +2645,16 @@
         <v>46208</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F56" s="13" t="n">
         <v>5800</v>
@@ -2384,16 +2665,16 @@
         <v>46208</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F57" s="13" t="n">
         <v>450</v>
@@ -2404,16 +2685,16 @@
         <v>46209</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F58" s="13" t="n">
         <v>120</v>
@@ -2424,16 +2705,16 @@
         <v>46209</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F59" s="13" t="n">
         <v>2100</v>
@@ -2444,16 +2725,16 @@
         <v>46211</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F60" s="13" t="n">
         <v>60</v>
@@ -2464,16 +2745,16 @@
         <v>46213</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F61" s="13" t="n">
         <v>320</v>
@@ -2484,16 +2765,16 @@
         <v>46214</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F62" s="13" t="n">
         <v>280</v>
@@ -2504,16 +2785,16 @@
         <v>46214</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F63" s="13" t="n">
         <v>229.01</v>
@@ -2524,16 +2805,16 @@
         <v>46214</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F64" s="13" t="n">
         <v>382.42</v>
@@ -2544,16 +2825,16 @@
         <v>46218</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F65" s="13" t="n">
         <v>1200</v>
@@ -2564,16 +2845,16 @@
         <v>46218</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F66" s="13" t="n">
         <v>280</v>
@@ -2584,16 +2865,16 @@
         <v>46219</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F67" s="13" t="n">
         <v>580</v>
@@ -2604,16 +2885,16 @@
         <v>46219</v>
       </c>
       <c r="B68" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="D68" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F68" s="13" t="n">
         <v>138.42</v>
@@ -2624,16 +2905,16 @@
         <v>46220</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F69" s="13" t="n">
         <v>55</v>
@@ -2644,16 +2925,16 @@
         <v>46222</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F70" s="13" t="n">
         <v>738.16</v>
@@ -2664,16 +2945,16 @@
         <v>46223</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F71" s="13" t="n">
         <v>303.02</v>
@@ -2684,16 +2965,16 @@
         <v>46225</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F72" s="13" t="n">
         <v>120</v>
@@ -2704,16 +2985,16 @@
         <v>46226</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F73" s="13" t="n">
         <v>509.37</v>
@@ -2724,16 +3005,16 @@
         <v>46227</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F74" s="13" t="n">
         <v>299.86</v>
@@ -2744,16 +3025,16 @@
         <v>46228</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F75" s="13" t="n">
         <v>480</v>
@@ -2764,16 +3045,16 @@
         <v>46229</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F76" s="13" t="n">
         <v>650</v>
@@ -2784,16 +3065,16 @@
         <v>46230</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F77" s="13" t="n">
         <v>90</v>
@@ -2804,16 +3085,16 @@
         <v>46235</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F78" s="13" t="n">
         <v>1914.02</v>
@@ -2824,16 +3105,16 @@
         <v>46237</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F79" s="13" t="n">
         <v>289</v>
@@ -2844,16 +3125,16 @@
         <v>46238</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F80" s="13" t="n">
         <v>90</v>
@@ -2864,16 +3145,16 @@
         <v>46239</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F81" s="13" t="n">
         <v>8200</v>
@@ -2884,16 +3165,16 @@
         <v>46239</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F82" s="13" t="n">
         <v>5800</v>
@@ -2904,16 +3185,16 @@
         <v>46239</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F83" s="13" t="n">
         <v>450</v>
@@ -2924,16 +3205,16 @@
         <v>46243</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F84" s="13" t="n">
         <v>55</v>
@@ -2944,16 +3225,16 @@
         <v>46244</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F85" s="13" t="n">
         <v>320</v>
@@ -2964,16 +3245,16 @@
         <v>46246</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F86" s="13" t="n">
         <v>60</v>
@@ -2984,16 +3265,16 @@
         <v>46246</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F87" s="13" t="n">
         <v>120</v>
@@ -3004,16 +3285,16 @@
         <v>46246</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F88" s="13" t="n">
         <v>576.69</v>
@@ -3024,16 +3305,16 @@
         <v>46247</v>
       </c>
       <c r="B89" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C89" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="D89" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F89" s="13" t="n">
         <v>164.47</v>
@@ -3044,16 +3325,16 @@
         <v>46249</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F90" s="13" t="n">
         <v>1200</v>
@@ -3064,16 +3345,16 @@
         <v>46249</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F91" s="13" t="n">
         <v>242.8</v>
@@ -3084,16 +3365,16 @@
         <v>46249</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F92" s="13" t="n">
         <v>280</v>
@@ -3104,16 +3385,16 @@
         <v>46250</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F93" s="13" t="n">
         <v>120</v>
@@ -3124,16 +3405,16 @@
         <v>46250</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F94" s="13" t="n">
         <v>580</v>
@@ -3144,16 +3425,16 @@
         <v>46250</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F95" s="13" t="n">
         <v>337.43</v>
@@ -3164,16 +3445,16 @@
         <v>46253</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F96" s="13" t="n">
         <v>512.44</v>
@@ -3184,16 +3465,16 @@
         <v>46254</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F97" s="13" t="n">
         <v>650</v>
@@ -3204,16 +3485,16 @@
         <v>46255</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F98" s="13" t="n">
         <v>210.24</v>
@@ -3224,16 +3505,16 @@
         <v>46256</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F99" s="13" t="n">
         <v>253.8</v>
@@ -3244,16 +3525,16 @@
         <v>46256</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F100" s="13" t="n">
         <v>2100</v>
@@ -3264,16 +3545,16 @@
         <v>46257</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F101" s="13" t="n">
         <v>280</v>
@@ -3284,16 +3565,16 @@
         <v>46258</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F102" s="13" t="n">
         <v>275.15</v>
@@ -3304,16 +3585,16 @@
         <v>46261</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F103" s="13" t="n">
         <v>480</v>
@@ -3324,16 +3605,16 @@
         <v>46268</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F104" s="13" t="n">
         <v>580</v>
@@ -3344,16 +3625,16 @@
         <v>46270</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F105" s="13" t="n">
         <v>8200</v>
@@ -3364,16 +3645,16 @@
         <v>46270</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F106" s="13" t="n">
         <v>5800</v>
@@ -3384,16 +3665,16 @@
         <v>46270</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F107" s="13" t="n">
         <v>120</v>
@@ -3404,16 +3685,16 @@
         <v>46270</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F108" s="13" t="n">
         <v>450</v>
@@ -3424,16 +3705,16 @@
         <v>46271</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F109" s="13" t="n">
         <v>280</v>
@@ -3444,16 +3725,16 @@
         <v>46271</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F110" s="13" t="n">
         <v>572.34</v>
@@ -3464,16 +3745,16 @@
         <v>46273</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F111" s="13" t="n">
         <v>1408.59</v>
@@ -3484,16 +3765,16 @@
         <v>46273</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F112" s="13" t="n">
         <v>329.93</v>
@@ -3504,16 +3785,16 @@
         <v>46274</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F113" s="13" t="n">
         <v>293.34</v>
@@ -3524,16 +3805,16 @@
         <v>46274</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F114" s="13" t="n">
         <v>480</v>
@@ -3544,16 +3825,16 @@
         <v>46275</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F115" s="13" t="n">
         <v>650</v>
@@ -3564,16 +3845,16 @@
         <v>46275</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F116" s="13" t="n">
         <v>320</v>
@@ -3584,16 +3865,16 @@
         <v>46277</v>
       </c>
       <c r="B117" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C117" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C117" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="D117" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F117" s="13" t="n">
         <v>153.03</v>
@@ -3604,16 +3885,16 @@
         <v>46278</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F118" s="13" t="n">
         <v>296.68</v>
@@ -3624,16 +3905,16 @@
         <v>46278</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F119" s="13" t="n">
         <v>120</v>
@@ -3644,16 +3925,16 @@
         <v>46280</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F120" s="13" t="n">
         <v>1200</v>
@@ -3664,16 +3945,16 @@
         <v>46280</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F121" s="13" t="n">
         <v>294.2</v>
@@ -3684,16 +3965,16 @@
         <v>46280</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F122" s="13" t="n">
         <v>280</v>
@@ -3704,16 +3985,16 @@
         <v>46281</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F123" s="13" t="n">
         <v>55</v>
@@ -3724,16 +4005,16 @@
         <v>46283</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F124" s="13" t="n">
         <v>2100</v>
@@ -3744,16 +4025,16 @@
         <v>46287</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F125" s="13" t="n">
         <v>90</v>
@@ -3764,16 +4045,16 @@
         <v>46288</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F126" s="13" t="n">
         <v>256.39</v>
@@ -3784,16 +4065,16 @@
         <v>46289</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F127" s="13" t="n">
         <v>413.57</v>
@@ -3804,16 +4085,16 @@
         <v>46290</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E128" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F128" s="13" t="n">
         <v>60</v>
@@ -3824,16 +4105,16 @@
         <v>46292</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F129" s="13" t="n">
         <v>198.44</v>
@@ -3844,16 +4125,16 @@
         <v>46297</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F130" s="13" t="n">
         <v>200.53</v>
@@ -3864,16 +4145,16 @@
         <v>46297</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F131" s="13" t="n">
         <v>1433.99</v>
@@ -3884,16 +4165,16 @@
         <v>46299</v>
       </c>
       <c r="B132" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C132" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C132" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="D132" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F132" s="13" t="n">
         <v>141.77</v>
@@ -3904,16 +4185,16 @@
         <v>46299</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F133" s="13" t="n">
         <v>90</v>
@@ -3924,16 +4205,16 @@
         <v>46300</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F134" s="13" t="n">
         <v>8200</v>
@@ -3944,16 +4225,16 @@
         <v>46300</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F135" s="13" t="n">
         <v>5800</v>
@@ -3964,16 +4245,16 @@
         <v>46300</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F136" s="13" t="n">
         <v>328.86</v>
@@ -3984,16 +4265,16 @@
         <v>46300</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E137" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F137" s="13" t="n">
         <v>450</v>
@@ -4004,16 +4285,16 @@
         <v>46301</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F138" s="13" t="n">
         <v>650</v>
@@ -4024,16 +4305,16 @@
         <v>46302</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F139" s="13" t="n">
         <v>647.56</v>
@@ -4044,16 +4325,16 @@
         <v>46304</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F140" s="13" t="n">
         <v>120</v>
@@ -4064,16 +4345,16 @@
         <v>46305</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E141" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F141" s="13" t="n">
         <v>369.74</v>
@@ -4084,16 +4365,16 @@
         <v>46305</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E142" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F142" s="13" t="n">
         <v>320</v>
@@ -4104,16 +4385,16 @@
         <v>46306</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E143" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F143" s="13" t="n">
         <v>280</v>
@@ -4124,16 +4405,16 @@
         <v>46306</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F144" s="13" t="n">
         <v>424.12</v>
@@ -4144,16 +4425,16 @@
         <v>46308</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F145" s="13" t="n">
         <v>480</v>
@@ -4164,16 +4445,16 @@
         <v>46308</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F146" s="13" t="n">
         <v>254.69</v>
@@ -4184,16 +4465,16 @@
         <v>46308</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F147" s="13" t="n">
         <v>120</v>
@@ -4204,16 +4485,16 @@
         <v>46309</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F148" s="13" t="n">
         <v>258.46</v>
@@ -4224,16 +4505,16 @@
         <v>46310</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F149" s="13" t="n">
         <v>1200</v>
@@ -4244,16 +4525,16 @@
         <v>46310</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F150" s="13" t="n">
         <v>280</v>
@@ -4264,16 +4545,16 @@
         <v>46312</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F151" s="13" t="n">
         <v>300.02</v>
@@ -4284,16 +4565,16 @@
         <v>46313</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F152" s="13" t="n">
         <v>2100</v>
@@ -4304,16 +4585,16 @@
         <v>46314</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F153" s="13" t="n">
         <v>60</v>
@@ -4324,16 +4605,16 @@
         <v>46314</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F154" s="13" t="n">
         <v>580</v>
@@ -4344,16 +4625,16 @@
         <v>46315</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F155" s="13" t="n">
         <v>55</v>
@@ -4398,47 +4679,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>13</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>8200</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
       <c r="G2" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="15" t="n">
         <f aca="false">IF(C2="","",IF(D2="Mensal",C2,IF(D2="Anual",C2/12,0)))</f>
@@ -4447,23 +4728,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1200</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" s="14"/>
       <c r="F3" s="14" t="n">
         <v>46539</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H3" s="15" t="n">
         <f aca="false">IF(C3="","",IF(D3="Mensal",C3,IF(D3="Anual",C3/12,0)))</f>
@@ -4472,23 +4753,23 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>8200</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>46357</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H4" s="15" t="n">
         <f aca="false">IF(C4="","",IF(D4="Mensal",C4,IF(D4="Anual",C4/12,0)))</f>
@@ -4497,23 +4778,23 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>2733</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E5" s="14" t="n">
         <v>46388</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="15" t="n">
         <f aca="false">IF(C5="","",IF(D5="Mensal",C5,IF(D5="Anual",C5/12,0)))</f>
@@ -4522,23 +4803,23 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1500</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" s="14" t="n">
         <v>46508</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(C6="","",IF(D6="Mensal",C6,IF(D6="Anual",C6/12,0)))</f>
@@ -5299,47 +5580,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" s="16" t="s">
         <v>13</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>5800</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
       <c r="G2" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="15" t="n">
         <f aca="false">IF(C2="","",IF(D2="Mensal",C2,IF(D2="Anual",C2/12,0)))</f>
@@ -5348,23 +5629,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>5800</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>46357</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" s="15" t="n">
         <f aca="false">IF(C3="","",IF(D3="Mensal",C3,IF(D3="Anual",C3/12,0)))</f>
@@ -5373,23 +5654,23 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1933</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>46569</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H4" s="15" t="n">
         <f aca="false">IF(C4="","",IF(D4="Mensal",C4,IF(D4="Anual",C4/12,0)))</f>
@@ -6163,7 +6444,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -6173,222 +6454,241 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D2" s="13" t="n">
         <v>60</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
       <c r="H2" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2" s="15" t="n">
         <f aca="false">IF(D2="","",IF(E2="Mensal",D2,IF(E2="Anual",D2/12,0)))</f>
         <v>60</v>
       </c>
+      <c r="J2" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3" s="13" t="n">
         <v>650</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="15" t="n">
         <f aca="false">IF(D3="","",IF(E3="Mensal",D3,IF(E3="Anual",D3/12,0)))</f>
         <v>650</v>
       </c>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>57</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>120</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
       <c r="H4" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="15" t="n">
         <f aca="false">IF(D4="","",IF(E4="Mensal",D4,IF(E4="Anual",D4/12,0)))</f>
         <v>120</v>
       </c>
+      <c r="J4" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>450</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="15" t="n">
         <f aca="false">IF(D5="","",IF(E5="Mensal",D5,IF(E5="Anual",D5/12,0)))</f>
         <v>450</v>
       </c>
+      <c r="J5" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>250</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="15" t="n">
         <f aca="false">IF(D6="","",IF(E6="Mensal",D6,IF(E6="Anual",D6/12,0)))</f>
         <v>250</v>
       </c>
+      <c r="J6" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>59</v>
-      </c>
       <c r="C7" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>2400</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7" s="14" t="n">
         <v>46447</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="15" t="n">
         <f aca="false">IF(D7="","",IF(E7="Mensal",D7,IF(E7="Anual",D7/12,0)))</f>
         <v>200</v>
       </c>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>1800</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>46388</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" s="15" t="n">
         <f aca="false">IF(D8="","",IF(E8="Mensal",D8,IF(E8="Anual",D8/12,0)))</f>
         <v>150</v>
       </c>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12"/>
@@ -6403,6 +6703,7 @@
         <f aca="false">IF(D9="","",IF(E9="Mensal",D9,IF(E9="Anual",D9/12,0)))</f>
         <v/>
       </c>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12"/>
@@ -6417,6 +6718,7 @@
         <f aca="false">IF(D10="","",IF(E10="Mensal",D10,IF(E10="Anual",D10/12,0)))</f>
         <v/>
       </c>
+      <c r="J10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12"/>
@@ -6431,6 +6733,7 @@
         <f aca="false">IF(D11="","",IF(E11="Mensal",D11,IF(E11="Anual",D11/12,0)))</f>
         <v/>
       </c>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12"/>
@@ -6445,6 +6748,7 @@
         <f aca="false">IF(D12="","",IF(E12="Mensal",D12,IF(E12="Anual",D12/12,0)))</f>
         <v/>
       </c>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12"/>
@@ -6459,6 +6763,7 @@
         <f aca="false">IF(D13="","",IF(E13="Mensal",D13,IF(E13="Anual",D13/12,0)))</f>
         <v/>
       </c>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12"/>
@@ -6473,6 +6778,7 @@
         <f aca="false">IF(D14="","",IF(E14="Mensal",D14,IF(E14="Anual",D14/12,0)))</f>
         <v/>
       </c>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12"/>
@@ -6487,6 +6793,7 @@
         <f aca="false">IF(D15="","",IF(E15="Mensal",D15,IF(E15="Anual",D15/12,0)))</f>
         <v/>
       </c>
+      <c r="J15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12"/>
@@ -6501,6 +6808,7 @@
         <f aca="false">IF(D16="","",IF(E16="Mensal",D16,IF(E16="Anual",D16/12,0)))</f>
         <v/>
       </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12"/>
@@ -6515,6 +6823,7 @@
         <f aca="false">IF(D17="","",IF(E17="Mensal",D17,IF(E17="Anual",D17/12,0)))</f>
         <v/>
       </c>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
@@ -6529,6 +6838,7 @@
         <f aca="false">IF(D18="","",IF(E18="Mensal",D18,IF(E18="Anual",D18/12,0)))</f>
         <v/>
       </c>
+      <c r="J18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
@@ -6543,6 +6853,7 @@
         <f aca="false">IF(D19="","",IF(E19="Mensal",D19,IF(E19="Anual",D19/12,0)))</f>
         <v/>
       </c>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
@@ -6557,6 +6868,7 @@
         <f aca="false">IF(D20="","",IF(E20="Mensal",D20,IF(E20="Anual",D20/12,0)))</f>
         <v/>
       </c>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12"/>
@@ -6571,6 +6883,7 @@
         <f aca="false">IF(D21="","",IF(E21="Mensal",D21,IF(E21="Anual",D21/12,0)))</f>
         <v/>
       </c>
+      <c r="J21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12"/>
@@ -6585,6 +6898,7 @@
         <f aca="false">IF(D22="","",IF(E22="Mensal",D22,IF(E22="Anual",D22/12,0)))</f>
         <v/>
       </c>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12"/>
@@ -6599,6 +6913,7 @@
         <f aca="false">IF(D23="","",IF(E23="Mensal",D23,IF(E23="Anual",D23/12,0)))</f>
         <v/>
       </c>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12"/>
@@ -6613,6 +6928,7 @@
         <f aca="false">IF(D24="","",IF(E24="Mensal",D24,IF(E24="Anual",D24/12,0)))</f>
         <v/>
       </c>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12"/>
@@ -6627,6 +6943,7 @@
         <f aca="false">IF(D25="","",IF(E25="Mensal",D25,IF(E25="Anual",D25/12,0)))</f>
         <v/>
       </c>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12"/>
@@ -6641,6 +6958,7 @@
         <f aca="false">IF(D26="","",IF(E26="Mensal",D26,IF(E26="Anual",D26/12,0)))</f>
         <v/>
       </c>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12"/>
@@ -6655,6 +6973,7 @@
         <f aca="false">IF(D27="","",IF(E27="Mensal",D27,IF(E27="Anual",D27/12,0)))</f>
         <v/>
       </c>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
@@ -6669,6 +6988,7 @@
         <f aca="false">IF(D28="","",IF(E28="Mensal",D28,IF(E28="Anual",D28/12,0)))</f>
         <v/>
       </c>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12"/>
@@ -6683,6 +7003,7 @@
         <f aca="false">IF(D29="","",IF(E29="Mensal",D29,IF(E29="Anual",D29/12,0)))</f>
         <v/>
       </c>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12"/>
@@ -6697,6 +7018,7 @@
         <f aca="false">IF(D30="","",IF(E30="Mensal",D30,IF(E30="Anual",D30/12,0)))</f>
         <v/>
       </c>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12"/>
@@ -6711,6 +7033,7 @@
         <f aca="false">IF(D31="","",IF(E31="Mensal",D31,IF(E31="Anual",D31/12,0)))</f>
         <v/>
       </c>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12"/>
@@ -6725,6 +7048,7 @@
         <f aca="false">IF(D32="","",IF(E32="Mensal",D32,IF(E32="Anual",D32/12,0)))</f>
         <v/>
       </c>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12"/>
@@ -6739,6 +7063,7 @@
         <f aca="false">IF(D33="","",IF(E33="Mensal",D33,IF(E33="Anual",D33/12,0)))</f>
         <v/>
       </c>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12"/>
@@ -6753,6 +7078,7 @@
         <f aca="false">IF(D34="","",IF(E34="Mensal",D34,IF(E34="Anual",D34/12,0)))</f>
         <v/>
       </c>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12"/>
@@ -6767,6 +7093,7 @@
         <f aca="false">IF(D35="","",IF(E35="Mensal",D35,IF(E35="Anual",D35/12,0)))</f>
         <v/>
       </c>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12"/>
@@ -6781,6 +7108,7 @@
         <f aca="false">IF(D36="","",IF(E36="Mensal",D36,IF(E36="Anual",D36/12,0)))</f>
         <v/>
       </c>
+      <c r="J36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12"/>
@@ -6795,6 +7123,7 @@
         <f aca="false">IF(D37="","",IF(E37="Mensal",D37,IF(E37="Anual",D37/12,0)))</f>
         <v/>
       </c>
+      <c r="J37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12"/>
@@ -6809,6 +7138,7 @@
         <f aca="false">IF(D38="","",IF(E38="Mensal",D38,IF(E38="Anual",D38/12,0)))</f>
         <v/>
       </c>
+      <c r="J38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12"/>
@@ -6823,6 +7153,7 @@
         <f aca="false">IF(D39="","",IF(E39="Mensal",D39,IF(E39="Anual",D39/12,0)))</f>
         <v/>
       </c>
+      <c r="J39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12"/>
@@ -6837,6 +7168,7 @@
         <f aca="false">IF(D40="","",IF(E40="Mensal",D40,IF(E40="Anual",D40/12,0)))</f>
         <v/>
       </c>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12"/>
@@ -6851,6 +7183,7 @@
         <f aca="false">IF(D41="","",IF(E41="Mensal",D41,IF(E41="Anual",D41/12,0)))</f>
         <v/>
       </c>
+      <c r="J41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12"/>
@@ -6865,6 +7198,7 @@
         <f aca="false">IF(D42="","",IF(E42="Mensal",D42,IF(E42="Anual",D42/12,0)))</f>
         <v/>
       </c>
+      <c r="J42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
@@ -6879,6 +7213,7 @@
         <f aca="false">IF(D43="","",IF(E43="Mensal",D43,IF(E43="Anual",D43/12,0)))</f>
         <v/>
       </c>
+      <c r="J43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
@@ -6893,6 +7228,7 @@
         <f aca="false">IF(D44="","",IF(E44="Mensal",D44,IF(E44="Anual",D44/12,0)))</f>
         <v/>
       </c>
+      <c r="J44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12"/>
@@ -6907,6 +7243,7 @@
         <f aca="false">IF(D45="","",IF(E45="Mensal",D45,IF(E45="Anual",D45/12,0)))</f>
         <v/>
       </c>
+      <c r="J45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12"/>
@@ -6921,6 +7258,7 @@
         <f aca="false">IF(D46="","",IF(E46="Mensal",D46,IF(E46="Anual",D46/12,0)))</f>
         <v/>
       </c>
+      <c r="J46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12"/>
@@ -6935,6 +7273,7 @@
         <f aca="false">IF(D47="","",IF(E47="Mensal",D47,IF(E47="Anual",D47/12,0)))</f>
         <v/>
       </c>
+      <c r="J47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12"/>
@@ -6949,6 +7288,7 @@
         <f aca="false">IF(D48="","",IF(E48="Mensal",D48,IF(E48="Anual",D48/12,0)))</f>
         <v/>
       </c>
+      <c r="J48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12"/>
@@ -6963,6 +7303,7 @@
         <f aca="false">IF(D49="","",IF(E49="Mensal",D49,IF(E49="Anual",D49/12,0)))</f>
         <v/>
       </c>
+      <c r="J49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12"/>
@@ -6977,6 +7318,7 @@
         <f aca="false">IF(D50="","",IF(E50="Mensal",D50,IF(E50="Anual",D50/12,0)))</f>
         <v/>
       </c>
+      <c r="J50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12"/>
@@ -6991,6 +7333,7 @@
         <f aca="false">IF(D51="","",IF(E51="Mensal",D51,IF(E51="Anual",D51/12,0)))</f>
         <v/>
       </c>
+      <c r="J51" s="12"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12"/>
@@ -7005,6 +7348,7 @@
         <f aca="false">IF(D52="","",IF(E52="Mensal",D52,IF(E52="Anual",D52/12,0)))</f>
         <v/>
       </c>
+      <c r="J52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12"/>
@@ -7019,6 +7363,7 @@
         <f aca="false">IF(D53="","",IF(E53="Mensal",D53,IF(E53="Anual",D53/12,0)))</f>
         <v/>
       </c>
+      <c r="J53" s="12"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12"/>
@@ -7033,6 +7378,7 @@
         <f aca="false">IF(D54="","",IF(E54="Mensal",D54,IF(E54="Anual",D54/12,0)))</f>
         <v/>
       </c>
+      <c r="J54" s="12"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12"/>
@@ -7047,6 +7393,7 @@
         <f aca="false">IF(D55="","",IF(E55="Mensal",D55,IF(E55="Anual",D55/12,0)))</f>
         <v/>
       </c>
+      <c r="J55" s="12"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12"/>
@@ -7061,6 +7408,7 @@
         <f aca="false">IF(D56="","",IF(E56="Mensal",D56,IF(E56="Anual",D56/12,0)))</f>
         <v/>
       </c>
+      <c r="J56" s="12"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12"/>
@@ -7075,6 +7423,7 @@
         <f aca="false">IF(D57="","",IF(E57="Mensal",D57,IF(E57="Anual",D57/12,0)))</f>
         <v/>
       </c>
+      <c r="J57" s="12"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12"/>
@@ -7089,6 +7438,7 @@
         <f aca="false">IF(D58="","",IF(E58="Mensal",D58,IF(E58="Anual",D58/12,0)))</f>
         <v/>
       </c>
+      <c r="J58" s="12"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12"/>
@@ -7103,6 +7453,7 @@
         <f aca="false">IF(D59="","",IF(E59="Mensal",D59,IF(E59="Anual",D59/12,0)))</f>
         <v/>
       </c>
+      <c r="J59" s="12"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12"/>
@@ -7117,6 +7468,7 @@
         <f aca="false">IF(D60="","",IF(E60="Mensal",D60,IF(E60="Anual",D60/12,0)))</f>
         <v/>
       </c>
+      <c r="J60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12"/>
@@ -7131,9 +7483,10 @@
         <f aca="false">IF(D61="","",IF(E61="Mensal",D61,IF(E61="Anual",D61/12,0)))</f>
         <v/>
       </c>
+      <c r="J61" s="12"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C61" type="list">
       <formula1>"Fixa,Variável"</formula1>
       <formula2>0</formula2>
@@ -7144,6 +7497,10 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H61" type="list">
       <formula1>"Sim,Não"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J61" type="list">
+      <formula1>Cartões!$A$2:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -7162,7 +7519,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -7172,191 +7529,207 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="16" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D2" s="13" t="n">
         <v>55</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
       <c r="H2" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2" s="15" t="n">
         <f aca="false">IF(D2="","",IF(E2="Mensal",D2,IF(E2="Anual",D2/12,0)))</f>
         <v>55</v>
       </c>
+      <c r="J2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3" s="13" t="n">
         <v>580</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="15" t="n">
         <f aca="false">IF(D3="","",IF(E3="Mensal",D3,IF(E3="Anual",D3/12,0)))</f>
         <v>580</v>
       </c>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>280</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
       <c r="H4" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="15" t="n">
         <f aca="false">IF(D4="","",IF(E4="Mensal",D4,IF(E4="Anual",D4/12,0)))</f>
         <v>280</v>
       </c>
+      <c r="J4" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>300</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="15" t="n">
         <f aca="false">IF(D5="","",IF(E5="Mensal",D5,IF(E5="Anual",D5/12,0)))</f>
         <v>300</v>
       </c>
+      <c r="J5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>250</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="15" t="n">
         <f aca="false">IF(D6="","",IF(E6="Mensal",D6,IF(E6="Anual",D6/12,0)))</f>
         <v>250</v>
       </c>
+      <c r="J6" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>200</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="15" t="n">
         <f aca="false">IF(D7="","",IF(E7="Mensal",D7,IF(E7="Anual",D7/12,0)))</f>
         <v>200</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7372,6 +7745,7 @@
         <f aca="false">IF(D8="","",IF(E8="Mensal",D8,IF(E8="Anual",D8/12,0)))</f>
         <v/>
       </c>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12"/>
@@ -7386,6 +7760,7 @@
         <f aca="false">IF(D9="","",IF(E9="Mensal",D9,IF(E9="Anual",D9/12,0)))</f>
         <v/>
       </c>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12"/>
@@ -7400,6 +7775,7 @@
         <f aca="false">IF(D10="","",IF(E10="Mensal",D10,IF(E10="Anual",D10/12,0)))</f>
         <v/>
       </c>
+      <c r="J10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12"/>
@@ -7414,6 +7790,7 @@
         <f aca="false">IF(D11="","",IF(E11="Mensal",D11,IF(E11="Anual",D11/12,0)))</f>
         <v/>
       </c>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12"/>
@@ -7428,6 +7805,7 @@
         <f aca="false">IF(D12="","",IF(E12="Mensal",D12,IF(E12="Anual",D12/12,0)))</f>
         <v/>
       </c>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12"/>
@@ -7442,6 +7820,7 @@
         <f aca="false">IF(D13="","",IF(E13="Mensal",D13,IF(E13="Anual",D13/12,0)))</f>
         <v/>
       </c>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12"/>
@@ -7456,6 +7835,7 @@
         <f aca="false">IF(D14="","",IF(E14="Mensal",D14,IF(E14="Anual",D14/12,0)))</f>
         <v/>
       </c>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12"/>
@@ -7470,6 +7850,7 @@
         <f aca="false">IF(D15="","",IF(E15="Mensal",D15,IF(E15="Anual",D15/12,0)))</f>
         <v/>
       </c>
+      <c r="J15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12"/>
@@ -7484,6 +7865,7 @@
         <f aca="false">IF(D16="","",IF(E16="Mensal",D16,IF(E16="Anual",D16/12,0)))</f>
         <v/>
       </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12"/>
@@ -7498,6 +7880,7 @@
         <f aca="false">IF(D17="","",IF(E17="Mensal",D17,IF(E17="Anual",D17/12,0)))</f>
         <v/>
       </c>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
@@ -7512,6 +7895,7 @@
         <f aca="false">IF(D18="","",IF(E18="Mensal",D18,IF(E18="Anual",D18/12,0)))</f>
         <v/>
       </c>
+      <c r="J18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
@@ -7526,6 +7910,7 @@
         <f aca="false">IF(D19="","",IF(E19="Mensal",D19,IF(E19="Anual",D19/12,0)))</f>
         <v/>
       </c>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
@@ -7540,6 +7925,7 @@
         <f aca="false">IF(D20="","",IF(E20="Mensal",D20,IF(E20="Anual",D20/12,0)))</f>
         <v/>
       </c>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12"/>
@@ -7554,6 +7940,7 @@
         <f aca="false">IF(D21="","",IF(E21="Mensal",D21,IF(E21="Anual",D21/12,0)))</f>
         <v/>
       </c>
+      <c r="J21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12"/>
@@ -7568,6 +7955,7 @@
         <f aca="false">IF(D22="","",IF(E22="Mensal",D22,IF(E22="Anual",D22/12,0)))</f>
         <v/>
       </c>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12"/>
@@ -7582,6 +7970,7 @@
         <f aca="false">IF(D23="","",IF(E23="Mensal",D23,IF(E23="Anual",D23/12,0)))</f>
         <v/>
       </c>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12"/>
@@ -7596,6 +7985,7 @@
         <f aca="false">IF(D24="","",IF(E24="Mensal",D24,IF(E24="Anual",D24/12,0)))</f>
         <v/>
       </c>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12"/>
@@ -7610,6 +8000,7 @@
         <f aca="false">IF(D25="","",IF(E25="Mensal",D25,IF(E25="Anual",D25/12,0)))</f>
         <v/>
       </c>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12"/>
@@ -7624,6 +8015,7 @@
         <f aca="false">IF(D26="","",IF(E26="Mensal",D26,IF(E26="Anual",D26/12,0)))</f>
         <v/>
       </c>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12"/>
@@ -7638,6 +8030,7 @@
         <f aca="false">IF(D27="","",IF(E27="Mensal",D27,IF(E27="Anual",D27/12,0)))</f>
         <v/>
       </c>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
@@ -7652,6 +8045,7 @@
         <f aca="false">IF(D28="","",IF(E28="Mensal",D28,IF(E28="Anual",D28/12,0)))</f>
         <v/>
       </c>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12"/>
@@ -7666,6 +8060,7 @@
         <f aca="false">IF(D29="","",IF(E29="Mensal",D29,IF(E29="Anual",D29/12,0)))</f>
         <v/>
       </c>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12"/>
@@ -7680,6 +8075,7 @@
         <f aca="false">IF(D30="","",IF(E30="Mensal",D30,IF(E30="Anual",D30/12,0)))</f>
         <v/>
       </c>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12"/>
@@ -7694,6 +8090,7 @@
         <f aca="false">IF(D31="","",IF(E31="Mensal",D31,IF(E31="Anual",D31/12,0)))</f>
         <v/>
       </c>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12"/>
@@ -7708,6 +8105,7 @@
         <f aca="false">IF(D32="","",IF(E32="Mensal",D32,IF(E32="Anual",D32/12,0)))</f>
         <v/>
       </c>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12"/>
@@ -7722,6 +8120,7 @@
         <f aca="false">IF(D33="","",IF(E33="Mensal",D33,IF(E33="Anual",D33/12,0)))</f>
         <v/>
       </c>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12"/>
@@ -7736,6 +8135,7 @@
         <f aca="false">IF(D34="","",IF(E34="Mensal",D34,IF(E34="Anual",D34/12,0)))</f>
         <v/>
       </c>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12"/>
@@ -7750,6 +8150,7 @@
         <f aca="false">IF(D35="","",IF(E35="Mensal",D35,IF(E35="Anual",D35/12,0)))</f>
         <v/>
       </c>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12"/>
@@ -7764,6 +8165,7 @@
         <f aca="false">IF(D36="","",IF(E36="Mensal",D36,IF(E36="Anual",D36/12,0)))</f>
         <v/>
       </c>
+      <c r="J36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12"/>
@@ -7778,6 +8180,7 @@
         <f aca="false">IF(D37="","",IF(E37="Mensal",D37,IF(E37="Anual",D37/12,0)))</f>
         <v/>
       </c>
+      <c r="J37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12"/>
@@ -7792,6 +8195,7 @@
         <f aca="false">IF(D38="","",IF(E38="Mensal",D38,IF(E38="Anual",D38/12,0)))</f>
         <v/>
       </c>
+      <c r="J38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12"/>
@@ -7806,6 +8210,7 @@
         <f aca="false">IF(D39="","",IF(E39="Mensal",D39,IF(E39="Anual",D39/12,0)))</f>
         <v/>
       </c>
+      <c r="J39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12"/>
@@ -7820,6 +8225,7 @@
         <f aca="false">IF(D40="","",IF(E40="Mensal",D40,IF(E40="Anual",D40/12,0)))</f>
         <v/>
       </c>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12"/>
@@ -7834,6 +8240,7 @@
         <f aca="false">IF(D41="","",IF(E41="Mensal",D41,IF(E41="Anual",D41/12,0)))</f>
         <v/>
       </c>
+      <c r="J41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12"/>
@@ -7848,6 +8255,7 @@
         <f aca="false">IF(D42="","",IF(E42="Mensal",D42,IF(E42="Anual",D42/12,0)))</f>
         <v/>
       </c>
+      <c r="J42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
@@ -7862,6 +8270,7 @@
         <f aca="false">IF(D43="","",IF(E43="Mensal",D43,IF(E43="Anual",D43/12,0)))</f>
         <v/>
       </c>
+      <c r="J43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
@@ -7876,6 +8285,7 @@
         <f aca="false">IF(D44="","",IF(E44="Mensal",D44,IF(E44="Anual",D44/12,0)))</f>
         <v/>
       </c>
+      <c r="J44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12"/>
@@ -7890,6 +8300,7 @@
         <f aca="false">IF(D45="","",IF(E45="Mensal",D45,IF(E45="Anual",D45/12,0)))</f>
         <v/>
       </c>
+      <c r="J45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12"/>
@@ -7904,6 +8315,7 @@
         <f aca="false">IF(D46="","",IF(E46="Mensal",D46,IF(E46="Anual",D46/12,0)))</f>
         <v/>
       </c>
+      <c r="J46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12"/>
@@ -7918,6 +8330,7 @@
         <f aca="false">IF(D47="","",IF(E47="Mensal",D47,IF(E47="Anual",D47/12,0)))</f>
         <v/>
       </c>
+      <c r="J47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12"/>
@@ -7932,6 +8345,7 @@
         <f aca="false">IF(D48="","",IF(E48="Mensal",D48,IF(E48="Anual",D48/12,0)))</f>
         <v/>
       </c>
+      <c r="J48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12"/>
@@ -7946,6 +8360,7 @@
         <f aca="false">IF(D49="","",IF(E49="Mensal",D49,IF(E49="Anual",D49/12,0)))</f>
         <v/>
       </c>
+      <c r="J49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12"/>
@@ -7960,6 +8375,7 @@
         <f aca="false">IF(D50="","",IF(E50="Mensal",D50,IF(E50="Anual",D50/12,0)))</f>
         <v/>
       </c>
+      <c r="J50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12"/>
@@ -7974,6 +8390,7 @@
         <f aca="false">IF(D51="","",IF(E51="Mensal",D51,IF(E51="Anual",D51/12,0)))</f>
         <v/>
       </c>
+      <c r="J51" s="12"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12"/>
@@ -7988,6 +8405,7 @@
         <f aca="false">IF(D52="","",IF(E52="Mensal",D52,IF(E52="Anual",D52/12,0)))</f>
         <v/>
       </c>
+      <c r="J52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12"/>
@@ -8002,6 +8420,7 @@
         <f aca="false">IF(D53="","",IF(E53="Mensal",D53,IF(E53="Anual",D53/12,0)))</f>
         <v/>
       </c>
+      <c r="J53" s="12"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12"/>
@@ -8016,6 +8435,7 @@
         <f aca="false">IF(D54="","",IF(E54="Mensal",D54,IF(E54="Anual",D54/12,0)))</f>
         <v/>
       </c>
+      <c r="J54" s="12"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12"/>
@@ -8030,6 +8450,7 @@
         <f aca="false">IF(D55="","",IF(E55="Mensal",D55,IF(E55="Anual",D55/12,0)))</f>
         <v/>
       </c>
+      <c r="J55" s="12"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12"/>
@@ -8044,6 +8465,7 @@
         <f aca="false">IF(D56="","",IF(E56="Mensal",D56,IF(E56="Anual",D56/12,0)))</f>
         <v/>
       </c>
+      <c r="J56" s="12"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12"/>
@@ -8058,6 +8480,7 @@
         <f aca="false">IF(D57="","",IF(E57="Mensal",D57,IF(E57="Anual",D57/12,0)))</f>
         <v/>
       </c>
+      <c r="J57" s="12"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12"/>
@@ -8072,6 +8495,7 @@
         <f aca="false">IF(D58="","",IF(E58="Mensal",D58,IF(E58="Anual",D58/12,0)))</f>
         <v/>
       </c>
+      <c r="J58" s="12"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12"/>
@@ -8086,6 +8510,7 @@
         <f aca="false">IF(D59="","",IF(E59="Mensal",D59,IF(E59="Anual",D59/12,0)))</f>
         <v/>
       </c>
+      <c r="J59" s="12"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12"/>
@@ -8100,6 +8525,7 @@
         <f aca="false">IF(D60="","",IF(E60="Mensal",D60,IF(E60="Anual",D60/12,0)))</f>
         <v/>
       </c>
+      <c r="J60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12"/>
@@ -8114,9 +8540,10 @@
         <f aca="false">IF(D61="","",IF(E61="Mensal",D61,IF(E61="Anual",D61/12,0)))</f>
         <v/>
       </c>
+      <c r="J61" s="12"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C61" type="list">
       <formula1>"Fixa,Variável"</formula1>
       <formula2>0</formula2>
@@ -8127,6 +8554,10 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H61" type="list">
       <formula1>"Sim,Não"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J61" type="list">
+      <formula1>Cartões!$A$2:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -8145,7 +8576,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -8156,362 +8587,381 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="17" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D2" s="13" t="n">
         <v>2100</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
       <c r="H2" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J2" s="15" t="n">
         <f aca="false">IF(D2="","",IF(E2="Mensal",D2,IF(E2="Anual",D2/12,0)))</f>
         <v>2100</v>
       </c>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3" s="13" t="n">
         <v>480</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J3" s="15" t="n">
         <f aca="false">IF(D3="","",IF(E3="Mensal",D3,IF(E3="Anual",D3/12,0)))</f>
         <v>480</v>
       </c>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>260</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
       <c r="H4" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J4" s="15" t="n">
         <f aca="false">IF(D4="","",IF(E4="Mensal",D4,IF(E4="Anual",D4/12,0)))</f>
         <v>260</v>
       </c>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="C5" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>140</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J5" s="15" t="n">
         <f aca="false">IF(D5="","",IF(E5="Mensal",D5,IF(E5="Anual",D5/12,0)))</f>
         <v>140</v>
       </c>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>120</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J6" s="15" t="n">
         <f aca="false">IF(D6="","",IF(E6="Mensal",D6,IF(E6="Anual",D6/12,0)))</f>
         <v>120</v>
       </c>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>1600</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J7" s="15" t="n">
         <f aca="false">IF(D7="","",IF(E7="Mensal",D7,IF(E7="Anual",D7/12,0)))</f>
         <v>1600</v>
       </c>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>650</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
       <c r="H8" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J8" s="15" t="n">
         <f aca="false">IF(D8="","",IF(E8="Mensal",D8,IF(E8="Anual",D8/12,0)))</f>
         <v>650</v>
       </c>
+      <c r="K8" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>90</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
       <c r="H9" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J9" s="15" t="n">
         <f aca="false">IF(D9="","",IF(E9="Mensal",D9,IF(E9="Anual",D9/12,0)))</f>
         <v>90</v>
       </c>
+      <c r="K9" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>400</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
       <c r="H10" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J10" s="15" t="n">
         <f aca="false">IF(D10="","",IF(E10="Mensal",D10,IF(E10="Anual",D10/12,0)))</f>
         <v>400</v>
       </c>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>1200</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>46357</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J11" s="15" t="n">
         <f aca="false">IF(D11="","",IF(E11="Mensal",D11,IF(E11="Anual",D11/12,0)))</f>
         <v>0</v>
       </c>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>6000</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>46569</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J12" s="15" t="n">
         <f aca="false">IF(D12="","",IF(E12="Mensal",D12,IF(E12="Anual",D12/12,0)))</f>
         <v>0</v>
       </c>
+      <c r="K12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12"/>
@@ -8527,6 +8977,7 @@
         <f aca="false">IF(D13="","",IF(E13="Mensal",D13,IF(E13="Anual",D13/12,0)))</f>
         <v/>
       </c>
+      <c r="K13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12"/>
@@ -8542,6 +8993,7 @@
         <f aca="false">IF(D14="","",IF(E14="Mensal",D14,IF(E14="Anual",D14/12,0)))</f>
         <v/>
       </c>
+      <c r="K14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12"/>
@@ -8557,6 +9009,7 @@
         <f aca="false">IF(D15="","",IF(E15="Mensal",D15,IF(E15="Anual",D15/12,0)))</f>
         <v/>
       </c>
+      <c r="K15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12"/>
@@ -8572,6 +9025,7 @@
         <f aca="false">IF(D16="","",IF(E16="Mensal",D16,IF(E16="Anual",D16/12,0)))</f>
         <v/>
       </c>
+      <c r="K16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12"/>
@@ -8587,6 +9041,7 @@
         <f aca="false">IF(D17="","",IF(E17="Mensal",D17,IF(E17="Anual",D17/12,0)))</f>
         <v/>
       </c>
+      <c r="K17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
@@ -8602,6 +9057,7 @@
         <f aca="false">IF(D18="","",IF(E18="Mensal",D18,IF(E18="Anual",D18/12,0)))</f>
         <v/>
       </c>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
@@ -8617,6 +9073,7 @@
         <f aca="false">IF(D19="","",IF(E19="Mensal",D19,IF(E19="Anual",D19/12,0)))</f>
         <v/>
       </c>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
@@ -8632,6 +9089,7 @@
         <f aca="false">IF(D20="","",IF(E20="Mensal",D20,IF(E20="Anual",D20/12,0)))</f>
         <v/>
       </c>
+      <c r="K20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12"/>
@@ -8647,6 +9105,7 @@
         <f aca="false">IF(D21="","",IF(E21="Mensal",D21,IF(E21="Anual",D21/12,0)))</f>
         <v/>
       </c>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12"/>
@@ -8662,6 +9121,7 @@
         <f aca="false">IF(D22="","",IF(E22="Mensal",D22,IF(E22="Anual",D22/12,0)))</f>
         <v/>
       </c>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12"/>
@@ -8677,6 +9137,7 @@
         <f aca="false">IF(D23="","",IF(E23="Mensal",D23,IF(E23="Anual",D23/12,0)))</f>
         <v/>
       </c>
+      <c r="K23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12"/>
@@ -8692,6 +9153,7 @@
         <f aca="false">IF(D24="","",IF(E24="Mensal",D24,IF(E24="Anual",D24/12,0)))</f>
         <v/>
       </c>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12"/>
@@ -8707,6 +9169,7 @@
         <f aca="false">IF(D25="","",IF(E25="Mensal",D25,IF(E25="Anual",D25/12,0)))</f>
         <v/>
       </c>
+      <c r="K25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12"/>
@@ -8722,6 +9185,7 @@
         <f aca="false">IF(D26="","",IF(E26="Mensal",D26,IF(E26="Anual",D26/12,0)))</f>
         <v/>
       </c>
+      <c r="K26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12"/>
@@ -8737,6 +9201,7 @@
         <f aca="false">IF(D27="","",IF(E27="Mensal",D27,IF(E27="Anual",D27/12,0)))</f>
         <v/>
       </c>
+      <c r="K27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
@@ -8752,6 +9217,7 @@
         <f aca="false">IF(D28="","",IF(E28="Mensal",D28,IF(E28="Anual",D28/12,0)))</f>
         <v/>
       </c>
+      <c r="K28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12"/>
@@ -8767,6 +9233,7 @@
         <f aca="false">IF(D29="","",IF(E29="Mensal",D29,IF(E29="Anual",D29/12,0)))</f>
         <v/>
       </c>
+      <c r="K29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12"/>
@@ -8782,6 +9249,7 @@
         <f aca="false">IF(D30="","",IF(E30="Mensal",D30,IF(E30="Anual",D30/12,0)))</f>
         <v/>
       </c>
+      <c r="K30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12"/>
@@ -8797,6 +9265,7 @@
         <f aca="false">IF(D31="","",IF(E31="Mensal",D31,IF(E31="Anual",D31/12,0)))</f>
         <v/>
       </c>
+      <c r="K31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12"/>
@@ -8812,6 +9281,7 @@
         <f aca="false">IF(D32="","",IF(E32="Mensal",D32,IF(E32="Anual",D32/12,0)))</f>
         <v/>
       </c>
+      <c r="K32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12"/>
@@ -8827,6 +9297,7 @@
         <f aca="false">IF(D33="","",IF(E33="Mensal",D33,IF(E33="Anual",D33/12,0)))</f>
         <v/>
       </c>
+      <c r="K33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12"/>
@@ -8842,6 +9313,7 @@
         <f aca="false">IF(D34="","",IF(E34="Mensal",D34,IF(E34="Anual",D34/12,0)))</f>
         <v/>
       </c>
+      <c r="K34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12"/>
@@ -8857,6 +9329,7 @@
         <f aca="false">IF(D35="","",IF(E35="Mensal",D35,IF(E35="Anual",D35/12,0)))</f>
         <v/>
       </c>
+      <c r="K35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12"/>
@@ -8872,6 +9345,7 @@
         <f aca="false">IF(D36="","",IF(E36="Mensal",D36,IF(E36="Anual",D36/12,0)))</f>
         <v/>
       </c>
+      <c r="K36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12"/>
@@ -8887,6 +9361,7 @@
         <f aca="false">IF(D37="","",IF(E37="Mensal",D37,IF(E37="Anual",D37/12,0)))</f>
         <v/>
       </c>
+      <c r="K37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12"/>
@@ -8902,6 +9377,7 @@
         <f aca="false">IF(D38="","",IF(E38="Mensal",D38,IF(E38="Anual",D38/12,0)))</f>
         <v/>
       </c>
+      <c r="K38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12"/>
@@ -8917,6 +9393,7 @@
         <f aca="false">IF(D39="","",IF(E39="Mensal",D39,IF(E39="Anual",D39/12,0)))</f>
         <v/>
       </c>
+      <c r="K39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12"/>
@@ -8932,6 +9409,7 @@
         <f aca="false">IF(D40="","",IF(E40="Mensal",D40,IF(E40="Anual",D40/12,0)))</f>
         <v/>
       </c>
+      <c r="K40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12"/>
@@ -8947,6 +9425,7 @@
         <f aca="false">IF(D41="","",IF(E41="Mensal",D41,IF(E41="Anual",D41/12,0)))</f>
         <v/>
       </c>
+      <c r="K41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12"/>
@@ -8962,6 +9441,7 @@
         <f aca="false">IF(D42="","",IF(E42="Mensal",D42,IF(E42="Anual",D42/12,0)))</f>
         <v/>
       </c>
+      <c r="K42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
@@ -8977,6 +9457,7 @@
         <f aca="false">IF(D43="","",IF(E43="Mensal",D43,IF(E43="Anual",D43/12,0)))</f>
         <v/>
       </c>
+      <c r="K43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
@@ -8992,6 +9473,7 @@
         <f aca="false">IF(D44="","",IF(E44="Mensal",D44,IF(E44="Anual",D44/12,0)))</f>
         <v/>
       </c>
+      <c r="K44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12"/>
@@ -9007,6 +9489,7 @@
         <f aca="false">IF(D45="","",IF(E45="Mensal",D45,IF(E45="Anual",D45/12,0)))</f>
         <v/>
       </c>
+      <c r="K45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12"/>
@@ -9022,6 +9505,7 @@
         <f aca="false">IF(D46="","",IF(E46="Mensal",D46,IF(E46="Anual",D46/12,0)))</f>
         <v/>
       </c>
+      <c r="K46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12"/>
@@ -9037,6 +9521,7 @@
         <f aca="false">IF(D47="","",IF(E47="Mensal",D47,IF(E47="Anual",D47/12,0)))</f>
         <v/>
       </c>
+      <c r="K47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12"/>
@@ -9052,6 +9537,7 @@
         <f aca="false">IF(D48="","",IF(E48="Mensal",D48,IF(E48="Anual",D48/12,0)))</f>
         <v/>
       </c>
+      <c r="K48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12"/>
@@ -9067,6 +9553,7 @@
         <f aca="false">IF(D49="","",IF(E49="Mensal",D49,IF(E49="Anual",D49/12,0)))</f>
         <v/>
       </c>
+      <c r="K49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12"/>
@@ -9082,6 +9569,7 @@
         <f aca="false">IF(D50="","",IF(E50="Mensal",D50,IF(E50="Anual",D50/12,0)))</f>
         <v/>
       </c>
+      <c r="K50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12"/>
@@ -9097,6 +9585,7 @@
         <f aca="false">IF(D51="","",IF(E51="Mensal",D51,IF(E51="Anual",D51/12,0)))</f>
         <v/>
       </c>
+      <c r="K51" s="12"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12"/>
@@ -9112,6 +9601,7 @@
         <f aca="false">IF(D52="","",IF(E52="Mensal",D52,IF(E52="Anual",D52/12,0)))</f>
         <v/>
       </c>
+      <c r="K52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12"/>
@@ -9127,6 +9617,7 @@
         <f aca="false">IF(D53="","",IF(E53="Mensal",D53,IF(E53="Anual",D53/12,0)))</f>
         <v/>
       </c>
+      <c r="K53" s="12"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12"/>
@@ -9142,6 +9633,7 @@
         <f aca="false">IF(D54="","",IF(E54="Mensal",D54,IF(E54="Anual",D54/12,0)))</f>
         <v/>
       </c>
+      <c r="K54" s="12"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12"/>
@@ -9157,6 +9649,7 @@
         <f aca="false">IF(D55="","",IF(E55="Mensal",D55,IF(E55="Anual",D55/12,0)))</f>
         <v/>
       </c>
+      <c r="K55" s="12"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12"/>
@@ -9172,6 +9665,7 @@
         <f aca="false">IF(D56="","",IF(E56="Mensal",D56,IF(E56="Anual",D56/12,0)))</f>
         <v/>
       </c>
+      <c r="K56" s="12"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12"/>
@@ -9187,6 +9681,7 @@
         <f aca="false">IF(D57="","",IF(E57="Mensal",D57,IF(E57="Anual",D57/12,0)))</f>
         <v/>
       </c>
+      <c r="K57" s="12"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12"/>
@@ -9202,6 +9697,7 @@
         <f aca="false">IF(D58="","",IF(E58="Mensal",D58,IF(E58="Anual",D58/12,0)))</f>
         <v/>
       </c>
+      <c r="K58" s="12"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12"/>
@@ -9217,6 +9713,7 @@
         <f aca="false">IF(D59="","",IF(E59="Mensal",D59,IF(E59="Anual",D59/12,0)))</f>
         <v/>
       </c>
+      <c r="K59" s="12"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12"/>
@@ -9232,6 +9729,7 @@
         <f aca="false">IF(D60="","",IF(E60="Mensal",D60,IF(E60="Anual",D60/12,0)))</f>
         <v/>
       </c>
+      <c r="K60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12"/>
@@ -9247,9 +9745,10 @@
         <f aca="false">IF(D61="","",IF(E61="Mensal",D61,IF(E61="Anual",D61/12,0)))</f>
         <v/>
       </c>
+      <c r="K61" s="12"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C61" type="list">
       <formula1>"Fixa,Variável"</formula1>
       <formula2>0</formula2>
@@ -9264,6 +9763,10 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I61" type="list">
       <formula1>"Rodrigo,Esposa,Conta conjunta"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K61" type="list">
+      <formula1>Cartões!$A$2:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -9282,7 +9785,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -9293,43 +9796,47 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>17</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>92</v>
+        <v>97</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D2" s="13" t="n">
         <v>450</v>
@@ -9348,16 +9855,19 @@
         <f aca="false">IF(OR(F2="",E2=""),"",EDATE(F2,E2-1))</f>
         <v>46512</v>
       </c>
+      <c r="I2" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D3" s="13" t="n">
         <v>320</v>
@@ -9376,16 +9886,17 @@
         <f aca="false">IF(OR(F3="",E3=""),"",EDATE(F3,E3-1))</f>
         <v>46397</v>
       </c>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>280</v>
@@ -9403,6 +9914,9 @@
       <c r="H4" s="18" t="n">
         <f aca="false">IF(OR(F4="",E4=""),"",EDATE(F4,E4-1))</f>
         <v>46614</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9420,6 +9934,7 @@
         <f aca="false">IF(OR(F5="",E5=""),"",EDATE(F5,E5-1))</f>
         <v/>
       </c>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12"/>
@@ -9436,6 +9951,7 @@
         <f aca="false">IF(OR(F6="",E6=""),"",EDATE(F6,E6-1))</f>
         <v/>
       </c>
+      <c r="I6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12"/>
@@ -9452,6 +9968,7 @@
         <f aca="false">IF(OR(F7="",E7=""),"",EDATE(F7,E7-1))</f>
         <v/>
       </c>
+      <c r="I7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12"/>
@@ -9468,6 +9985,7 @@
         <f aca="false">IF(OR(F8="",E8=""),"",EDATE(F8,E8-1))</f>
         <v/>
       </c>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12"/>
@@ -9484,6 +10002,7 @@
         <f aca="false">IF(OR(F9="",E9=""),"",EDATE(F9,E9-1))</f>
         <v/>
       </c>
+      <c r="I9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12"/>
@@ -9500,6 +10019,7 @@
         <f aca="false">IF(OR(F10="",E10=""),"",EDATE(F10,E10-1))</f>
         <v/>
       </c>
+      <c r="I10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12"/>
@@ -9516,6 +10036,7 @@
         <f aca="false">IF(OR(F11="",E11=""),"",EDATE(F11,E11-1))</f>
         <v/>
       </c>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12"/>
@@ -9532,6 +10053,7 @@
         <f aca="false">IF(OR(F12="",E12=""),"",EDATE(F12,E12-1))</f>
         <v/>
       </c>
+      <c r="I12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12"/>
@@ -9548,6 +10070,7 @@
         <f aca="false">IF(OR(F13="",E13=""),"",EDATE(F13,E13-1))</f>
         <v/>
       </c>
+      <c r="I13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12"/>
@@ -9564,6 +10087,7 @@
         <f aca="false">IF(OR(F14="",E14=""),"",EDATE(F14,E14-1))</f>
         <v/>
       </c>
+      <c r="I14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12"/>
@@ -9580,6 +10104,7 @@
         <f aca="false">IF(OR(F15="",E15=""),"",EDATE(F15,E15-1))</f>
         <v/>
       </c>
+      <c r="I15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12"/>
@@ -9596,6 +10121,7 @@
         <f aca="false">IF(OR(F16="",E16=""),"",EDATE(F16,E16-1))</f>
         <v/>
       </c>
+      <c r="I16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12"/>
@@ -9612,6 +10138,7 @@
         <f aca="false">IF(OR(F17="",E17=""),"",EDATE(F17,E17-1))</f>
         <v/>
       </c>
+      <c r="I17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
@@ -9628,6 +10155,7 @@
         <f aca="false">IF(OR(F18="",E18=""),"",EDATE(F18,E18-1))</f>
         <v/>
       </c>
+      <c r="I18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
@@ -9644,6 +10172,7 @@
         <f aca="false">IF(OR(F19="",E19=""),"",EDATE(F19,E19-1))</f>
         <v/>
       </c>
+      <c r="I19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
@@ -9660,6 +10189,7 @@
         <f aca="false">IF(OR(F20="",E20=""),"",EDATE(F20,E20-1))</f>
         <v/>
       </c>
+      <c r="I20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12"/>
@@ -9676,6 +10206,7 @@
         <f aca="false">IF(OR(F21="",E21=""),"",EDATE(F21,E21-1))</f>
         <v/>
       </c>
+      <c r="I21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12"/>
@@ -9692,6 +10223,7 @@
         <f aca="false">IF(OR(F22="",E22=""),"",EDATE(F22,E22-1))</f>
         <v/>
       </c>
+      <c r="I22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12"/>
@@ -9708,6 +10240,7 @@
         <f aca="false">IF(OR(F23="",E23=""),"",EDATE(F23,E23-1))</f>
         <v/>
       </c>
+      <c r="I23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12"/>
@@ -9724,6 +10257,7 @@
         <f aca="false">IF(OR(F24="",E24=""),"",EDATE(F24,E24-1))</f>
         <v/>
       </c>
+      <c r="I24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12"/>
@@ -9740,6 +10274,7 @@
         <f aca="false">IF(OR(F25="",E25=""),"",EDATE(F25,E25-1))</f>
         <v/>
       </c>
+      <c r="I25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12"/>
@@ -9756,6 +10291,7 @@
         <f aca="false">IF(OR(F26="",E26=""),"",EDATE(F26,E26-1))</f>
         <v/>
       </c>
+      <c r="I26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12"/>
@@ -9772,6 +10308,7 @@
         <f aca="false">IF(OR(F27="",E27=""),"",EDATE(F27,E27-1))</f>
         <v/>
       </c>
+      <c r="I27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
@@ -9788,6 +10325,7 @@
         <f aca="false">IF(OR(F28="",E28=""),"",EDATE(F28,E28-1))</f>
         <v/>
       </c>
+      <c r="I28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12"/>
@@ -9804,6 +10342,7 @@
         <f aca="false">IF(OR(F29="",E29=""),"",EDATE(F29,E29-1))</f>
         <v/>
       </c>
+      <c r="I29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12"/>
@@ -9820,6 +10359,7 @@
         <f aca="false">IF(OR(F30="",E30=""),"",EDATE(F30,E30-1))</f>
         <v/>
       </c>
+      <c r="I30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12"/>
@@ -9836,6 +10376,7 @@
         <f aca="false">IF(OR(F31="",E31=""),"",EDATE(F31,E31-1))</f>
         <v/>
       </c>
+      <c r="I31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12"/>
@@ -9852,6 +10393,7 @@
         <f aca="false">IF(OR(F32="",E32=""),"",EDATE(F32,E32-1))</f>
         <v/>
       </c>
+      <c r="I32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12"/>
@@ -9868,6 +10410,7 @@
         <f aca="false">IF(OR(F33="",E33=""),"",EDATE(F33,E33-1))</f>
         <v/>
       </c>
+      <c r="I33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12"/>
@@ -9884,6 +10427,7 @@
         <f aca="false">IF(OR(F34="",E34=""),"",EDATE(F34,E34-1))</f>
         <v/>
       </c>
+      <c r="I34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12"/>
@@ -9900,6 +10444,7 @@
         <f aca="false">IF(OR(F35="",E35=""),"",EDATE(F35,E35-1))</f>
         <v/>
       </c>
+      <c r="I35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12"/>
@@ -9916,6 +10461,7 @@
         <f aca="false">IF(OR(F36="",E36=""),"",EDATE(F36,E36-1))</f>
         <v/>
       </c>
+      <c r="I36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12"/>
@@ -9932,6 +10478,7 @@
         <f aca="false">IF(OR(F37="",E37=""),"",EDATE(F37,E37-1))</f>
         <v/>
       </c>
+      <c r="I37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12"/>
@@ -9948,6 +10495,7 @@
         <f aca="false">IF(OR(F38="",E38=""),"",EDATE(F38,E38-1))</f>
         <v/>
       </c>
+      <c r="I38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12"/>
@@ -9964,6 +10512,7 @@
         <f aca="false">IF(OR(F39="",E39=""),"",EDATE(F39,E39-1))</f>
         <v/>
       </c>
+      <c r="I39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12"/>
@@ -9980,6 +10529,7 @@
         <f aca="false">IF(OR(F40="",E40=""),"",EDATE(F40,E40-1))</f>
         <v/>
       </c>
+      <c r="I40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12"/>
@@ -9996,6 +10546,7 @@
         <f aca="false">IF(OR(F41="",E41=""),"",EDATE(F41,E41-1))</f>
         <v/>
       </c>
+      <c r="I41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12"/>
@@ -10012,6 +10563,7 @@
         <f aca="false">IF(OR(F42="",E42=""),"",EDATE(F42,E42-1))</f>
         <v/>
       </c>
+      <c r="I42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
@@ -10028,6 +10580,7 @@
         <f aca="false">IF(OR(F43="",E43=""),"",EDATE(F43,E43-1))</f>
         <v/>
       </c>
+      <c r="I43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
@@ -10044,6 +10597,7 @@
         <f aca="false">IF(OR(F44="",E44=""),"",EDATE(F44,E44-1))</f>
         <v/>
       </c>
+      <c r="I44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12"/>
@@ -10060,6 +10614,7 @@
         <f aca="false">IF(OR(F45="",E45=""),"",EDATE(F45,E45-1))</f>
         <v/>
       </c>
+      <c r="I45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12"/>
@@ -10076,6 +10631,7 @@
         <f aca="false">IF(OR(F46="",E46=""),"",EDATE(F46,E46-1))</f>
         <v/>
       </c>
+      <c r="I46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12"/>
@@ -10092,6 +10648,7 @@
         <f aca="false">IF(OR(F47="",E47=""),"",EDATE(F47,E47-1))</f>
         <v/>
       </c>
+      <c r="I47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12"/>
@@ -10108,6 +10665,7 @@
         <f aca="false">IF(OR(F48="",E48=""),"",EDATE(F48,E48-1))</f>
         <v/>
       </c>
+      <c r="I48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12"/>
@@ -10124,6 +10682,7 @@
         <f aca="false">IF(OR(F49="",E49=""),"",EDATE(F49,E49-1))</f>
         <v/>
       </c>
+      <c r="I49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12"/>
@@ -10140,6 +10699,7 @@
         <f aca="false">IF(OR(F50="",E50=""),"",EDATE(F50,E50-1))</f>
         <v/>
       </c>
+      <c r="I50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12"/>
@@ -10156,6 +10716,7 @@
         <f aca="false">IF(OR(F51="",E51=""),"",EDATE(F51,E51-1))</f>
         <v/>
       </c>
+      <c r="I51" s="12"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12"/>
@@ -10172,6 +10733,7 @@
         <f aca="false">IF(OR(F52="",E52=""),"",EDATE(F52,E52-1))</f>
         <v/>
       </c>
+      <c r="I52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12"/>
@@ -10188,6 +10750,7 @@
         <f aca="false">IF(OR(F53="",E53=""),"",EDATE(F53,E53-1))</f>
         <v/>
       </c>
+      <c r="I53" s="12"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12"/>
@@ -10204,6 +10767,7 @@
         <f aca="false">IF(OR(F54="",E54=""),"",EDATE(F54,E54-1))</f>
         <v/>
       </c>
+      <c r="I54" s="12"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12"/>
@@ -10220,6 +10784,7 @@
         <f aca="false">IF(OR(F55="",E55=""),"",EDATE(F55,E55-1))</f>
         <v/>
       </c>
+      <c r="I55" s="12"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12"/>
@@ -10236,6 +10801,7 @@
         <f aca="false">IF(OR(F56="",E56=""),"",EDATE(F56,E56-1))</f>
         <v/>
       </c>
+      <c r="I56" s="12"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12"/>
@@ -10252,6 +10818,7 @@
         <f aca="false">IF(OR(F57="",E57=""),"",EDATE(F57,E57-1))</f>
         <v/>
       </c>
+      <c r="I57" s="12"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12"/>
@@ -10268,6 +10835,7 @@
         <f aca="false">IF(OR(F58="",E58=""),"",EDATE(F58,E58-1))</f>
         <v/>
       </c>
+      <c r="I58" s="12"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12"/>
@@ -10284,6 +10852,7 @@
         <f aca="false">IF(OR(F59="",E59=""),"",EDATE(F59,E59-1))</f>
         <v/>
       </c>
+      <c r="I59" s="12"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12"/>
@@ -10300,6 +10869,7 @@
         <f aca="false">IF(OR(F60="",E60=""),"",EDATE(F60,E60-1))</f>
         <v/>
       </c>
+      <c r="I60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12"/>
@@ -10316,11 +10886,16 @@
         <f aca="false">IF(OR(F61="",E61=""),"",EDATE(F61,E61-1))</f>
         <v/>
       </c>
+      <c r="I61" s="12"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C61" type="list">
       <formula1>"Rodrigo,Esposa,Casal"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I61" type="list">
+      <formula1>Cartões!$A$2:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -10350,29 +10925,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>15000</v>
@@ -10385,15 +10960,15 @@
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>8000</v>
@@ -10409,10 +10984,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>6000</v>
@@ -10961,229 +11536,330 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="10" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>111</v>
-      </c>
+      <c r="A2" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>114</v>
-      </c>
+      <c r="A3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>118</v>
-      </c>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>121</v>
-      </c>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>124</v>
-      </c>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>127</v>
-      </c>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>130</v>
-      </c>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>133</v>
-      </c>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="24" t="n">
-        <v>24</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>136</v>
-      </c>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>139</v>
-      </c>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>142</v>
-      </c>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>145</v>
-      </c>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>148</v>
-      </c>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>151</v>
-      </c>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4" type="list">
-      <formula1>"Proporcional à renda,Igual (50/50),Percentual fixo"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B2:B31" type="list">
+      <formula1>"Rodrigo,Esposa,Casal"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
